--- a/data/processed/asics_sentiment.xlsx
+++ b/data/processed/asics_sentiment.xlsx
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Leadership_context_human</t>
+          <t>Leadership_context</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Information_valence_human</t>
+          <t>Information_valence</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">

--- a/data/processed/asics_sentiment.xlsx
+++ b/data/processed/asics_sentiment.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z207"/>
+  <dimension ref="A1:AB207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,16 @@
           <t>finbert_n_chunks</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>financial_roberta_score</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>finbert_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -649,6 +659,12 @@
       <c r="Z2" t="n">
         <v>1</v>
       </c>
+      <c r="AA2" t="n">
+        <v>0.9970345166802872</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.2983057028613985</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,6 +767,12 @@
       <c r="Z3" t="n">
         <v>1</v>
       </c>
+      <c r="AA3" t="n">
+        <v>-0.0005399801884777844</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.03481552191078663</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -853,6 +875,12 @@
       <c r="Z4" t="n">
         <v>1</v>
       </c>
+      <c r="AA4" t="n">
+        <v>0.9285570973879658</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1572400480508804</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -955,6 +983,12 @@
       <c r="Z5" t="n">
         <v>1</v>
       </c>
+      <c r="AA5" t="n">
+        <v>0.001215501033584587</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1049100905656815</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1057,6 +1091,12 @@
       <c r="Z6" t="n">
         <v>1</v>
       </c>
+      <c r="AA6" t="n">
+        <v>0.8720547716366127</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1570949368178844</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1159,6 +1199,12 @@
       <c r="Z7" t="n">
         <v>1</v>
       </c>
+      <c r="AA7" t="n">
+        <v>0.9973841008613817</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5016811611130834</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1261,6 +1307,12 @@
       <c r="Z8" t="n">
         <v>1</v>
       </c>
+      <c r="AA8" t="n">
+        <v>0.01498483006434981</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.08764300122857094</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1363,6 +1415,12 @@
       <c r="Z9" t="n">
         <v>1</v>
       </c>
+      <c r="AA9" t="n">
+        <v>0.3027249810111243</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.07160060852766037</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1465,6 +1523,12 @@
       <c r="Z10" t="n">
         <v>1</v>
       </c>
+      <c r="AA10" t="n">
+        <v>0.4879195513785817</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1505449963733554</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1571,6 +1635,12 @@
       <c r="Z11" t="n">
         <v>1</v>
       </c>
+      <c r="AA11" t="n">
+        <v>0.9862838845001534</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.07624049764126539</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1673,6 +1743,12 @@
       <c r="Z12" t="n">
         <v>1</v>
       </c>
+      <c r="AA12" t="n">
+        <v>-0.1262614079751074</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.2029639091342688</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1775,6 +1851,12 @@
       <c r="Z13" t="n">
         <v>1</v>
       </c>
+      <c r="AA13" t="n">
+        <v>0.0001822337217163295</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.147567224688828</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1877,6 +1959,12 @@
       <c r="Z14" t="n">
         <v>1</v>
       </c>
+      <c r="AA14" t="n">
+        <v>-0.0004567128198686987</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.01884541846811771</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1979,6 +2067,12 @@
       <c r="Z15" t="n">
         <v>1</v>
       </c>
+      <c r="AA15" t="n">
+        <v>0.9976739641861059</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.7227157447487116</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2081,6 +2175,12 @@
       <c r="Z16" t="n">
         <v>1</v>
       </c>
+      <c r="AA16" t="n">
+        <v>0.8679739721847</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.5832089697942138</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2187,6 +2287,12 @@
       <c r="Z17" t="n">
         <v>1</v>
       </c>
+      <c r="AA17" t="n">
+        <v>0.9975398739334196</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8602702505886555</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2297,6 +2403,12 @@
       <c r="Z18" t="n">
         <v>1</v>
       </c>
+      <c r="AA18" t="n">
+        <v>0.9975074210960884</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.841106781270355</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2399,6 +2511,12 @@
       <c r="Z19" t="n">
         <v>1</v>
       </c>
+      <c r="AA19" t="n">
+        <v>0.002111049485392869</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.0151409488171339</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2501,6 +2619,12 @@
       <c r="Z20" t="n">
         <v>1</v>
       </c>
+      <c r="AA20" t="n">
+        <v>0.9975426580058411</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.7862707898020744</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2603,6 +2727,12 @@
       <c r="Z21" t="n">
         <v>1</v>
       </c>
+      <c r="AA21" t="n">
+        <v>0.9975742127280682</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5550833074375987</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2705,6 +2835,12 @@
       <c r="Z22" t="n">
         <v>1</v>
       </c>
+      <c r="AA22" t="n">
+        <v>0.9956354738387745</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.5187036236748099</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2807,6 +2943,12 @@
       <c r="Z23" t="n">
         <v>1</v>
       </c>
+      <c r="AA23" t="n">
+        <v>0.01475768929230981</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.137160412967205</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2909,6 +3051,12 @@
       <c r="Z24" t="n">
         <v>1</v>
       </c>
+      <c r="AA24" t="n">
+        <v>0.9959030553727644</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.1346531752496958</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3011,6 +3159,12 @@
       <c r="Z25" t="n">
         <v>1</v>
       </c>
+      <c r="AA25" t="n">
+        <v>0.9975485348841175</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.5537455026060343</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3114,6 +3268,12 @@
       <c r="Z26" t="n">
         <v>1</v>
       </c>
+      <c r="AA26" t="n">
+        <v>0.9963873135275207</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.09540391154587269</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3217,6 +3377,12 @@
       <c r="Z27" t="n">
         <v>1</v>
       </c>
+      <c r="AA27" t="n">
+        <v>0.9975944350007921</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.4079882698133588</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3320,6 +3486,12 @@
       <c r="Z28" t="n">
         <v>1</v>
       </c>
+      <c r="AA28" t="n">
+        <v>0.9975806911243126</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.6100926976650953</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3422,6 +3594,12 @@
       <c r="Z29" t="n">
         <v>1</v>
       </c>
+      <c r="AA29" t="n">
+        <v>0.0007276744800037704</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.08467329572886229</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3524,6 +3702,12 @@
       <c r="Z30" t="n">
         <v>1</v>
       </c>
+      <c r="AA30" t="n">
+        <v>0.6586348053533584</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.1021225610747933</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3626,6 +3810,12 @@
       <c r="Z31" t="n">
         <v>1</v>
       </c>
+      <c r="AA31" t="n">
+        <v>0.002125254599377513</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.02875936776399612</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3728,6 +3918,12 @@
       <c r="Z32" t="n">
         <v>1</v>
       </c>
+      <c r="AA32" t="n">
+        <v>-0.9986805431253742</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-0.954367246478796</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3830,6 +4026,12 @@
       <c r="Z33" t="n">
         <v>1</v>
       </c>
+      <c r="AA33" t="n">
+        <v>0.0005880184617126361</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.8866860084235668</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3932,6 +4134,12 @@
       <c r="Z34" t="n">
         <v>1</v>
       </c>
+      <c r="AA34" t="n">
+        <v>0.9976314243976958</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.8790194895118475</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4034,6 +4242,12 @@
       <c r="Z35" t="n">
         <v>1</v>
       </c>
+      <c r="AA35" t="n">
+        <v>0.9977025764528662</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.3801028607413173</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4136,6 +4350,12 @@
       <c r="Z36" t="n">
         <v>1</v>
       </c>
+      <c r="AA36" t="n">
+        <v>0.0005684149509761482</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>-0.002346944063901901</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4238,6 +4458,12 @@
       <c r="Z37" t="n">
         <v>1</v>
       </c>
+      <c r="AA37" t="n">
+        <v>0.9975440435810015</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.5151714282110333</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4340,6 +4566,12 @@
       <c r="Z38" t="n">
         <v>1</v>
       </c>
+      <c r="AA38" t="n">
+        <v>0.997719642939046</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.9017463643103838</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4442,6 +4674,12 @@
       <c r="Z39" t="n">
         <v>1</v>
       </c>
+      <c r="AA39" t="n">
+        <v>0.9976526813115925</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.7112265806645155</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4544,6 +4782,12 @@
       <c r="Z40" t="n">
         <v>1</v>
       </c>
+      <c r="AA40" t="n">
+        <v>0.9976053741411306</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.4142597988247871</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4646,6 +4890,12 @@
       <c r="Z41" t="n">
         <v>1</v>
       </c>
+      <c r="AA41" t="n">
+        <v>0.003812675713561475</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.8426183904521167</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4748,6 +4998,12 @@
       <c r="Z42" t="n">
         <v>1</v>
       </c>
+      <c r="AA42" t="n">
+        <v>0.9975224614026956</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.9185877977870405</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4850,6 +5106,12 @@
       <c r="Z43" t="n">
         <v>1</v>
       </c>
+      <c r="AA43" t="n">
+        <v>0.001154704281361774</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.02243106439709663</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4952,6 +5214,12 @@
       <c r="Z44" t="n">
         <v>1</v>
       </c>
+      <c r="AA44" t="n">
+        <v>0.00771306645765435</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.1177994962781668</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5054,6 +5322,12 @@
       <c r="Z45" t="n">
         <v>1</v>
       </c>
+      <c r="AA45" t="n">
+        <v>0.9974512802436948</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.1114023001864552</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5156,6 +5430,12 @@
       <c r="Z46" t="n">
         <v>1</v>
       </c>
+      <c r="AA46" t="n">
+        <v>-0.9925019950896967</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>-0.04343380406498909</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5258,6 +5538,12 @@
       <c r="Z47" t="n">
         <v>1</v>
       </c>
+      <c r="AA47" t="n">
+        <v>-0.1798422202700749</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>-0.01030772924423218</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5360,6 +5646,12 @@
       <c r="Z48" t="n">
         <v>1</v>
       </c>
+      <c r="AA48" t="n">
+        <v>0.9976376940030605</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.8086389265954494</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5462,6 +5754,12 @@
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AA49" t="n">
+        <v>-0.007883042329922318</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.1868892638012767</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5564,6 +5862,12 @@
       <c r="Z50" t="n">
         <v>1</v>
       </c>
+      <c r="AA50" t="n">
+        <v>-0.984433796533267</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-0.135182648897171</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5666,6 +5970,12 @@
       <c r="Z51" t="n">
         <v>1</v>
       </c>
+      <c r="AA51" t="n">
+        <v>0.03612622564833146</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.5462204869836569</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5768,6 +6078,12 @@
       <c r="Z52" t="n">
         <v>1</v>
       </c>
+      <c r="AA52" t="n">
+        <v>0.9892178555601276</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.04182502627372742</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5870,6 +6186,12 @@
       <c r="Z53" t="n">
         <v>1</v>
       </c>
+      <c r="AA53" t="n">
+        <v>0.9966796289081685</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.2573575424030423</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5972,6 +6294,12 @@
       <c r="Z54" t="n">
         <v>1</v>
       </c>
+      <c r="AA54" t="n">
+        <v>0.9931214585376438</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.2277068383991718</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6074,6 +6402,12 @@
       <c r="Z55" t="n">
         <v>1</v>
       </c>
+      <c r="AA55" t="n">
+        <v>0.9723920202523004</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.1391584109514952</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6176,6 +6510,12 @@
       <c r="Z56" t="n">
         <v>1</v>
       </c>
+      <c r="AA56" t="n">
+        <v>0.9971830054419115</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.4641476348042488</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6286,6 +6626,12 @@
       <c r="Z57" t="n">
         <v>1</v>
       </c>
+      <c r="AA57" t="n">
+        <v>0.9391388655349147</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.1250356854870915</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6388,6 +6734,12 @@
       <c r="Z58" t="n">
         <v>1</v>
       </c>
+      <c r="AA58" t="n">
+        <v>0.9972861974383704</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0.415188642218709</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6490,6 +6842,12 @@
       <c r="Z59" t="n">
         <v>1</v>
       </c>
+      <c r="AA59" t="n">
+        <v>0.9972463479498401</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.6887661032378674</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6592,6 +6950,12 @@
       <c r="Z60" t="n">
         <v>1</v>
       </c>
+      <c r="AA60" t="n">
+        <v>0.9975866593886167</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0.813620563596487</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6694,6 +7058,12 @@
       <c r="Z61" t="n">
         <v>1</v>
       </c>
+      <c r="AA61" t="n">
+        <v>0.007902869925601408</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>-0.01672414690256119</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6796,6 +7166,12 @@
       <c r="Z62" t="n">
         <v>1</v>
       </c>
+      <c r="AA62" t="n">
+        <v>0.9951525086071342</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0.3563030809164047</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6898,6 +7274,12 @@
       <c r="Z63" t="n">
         <v>1</v>
       </c>
+      <c r="AA63" t="n">
+        <v>0.9973817415884696</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0.9301554244011641</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7000,6 +7382,12 @@
       <c r="Z64" t="n">
         <v>1</v>
       </c>
+      <c r="AA64" t="n">
+        <v>0.001187334724818356</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0.23303247615695</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7102,6 +7490,12 @@
       <c r="Z65" t="n">
         <v>1</v>
       </c>
+      <c r="AA65" t="n">
+        <v>0.9974023174727336</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.8879679022356868</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7204,6 +7598,12 @@
       <c r="Z66" t="n">
         <v>1</v>
       </c>
+      <c r="AA66" t="n">
+        <v>0.1004838794469833</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>-0.1707835793495178</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7314,6 +7714,12 @@
       <c r="Z67" t="n">
         <v>1</v>
       </c>
+      <c r="AA67" t="n">
+        <v>0.9973791140364483</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0.2051482470706105</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7416,6 +7822,12 @@
       <c r="Z68" t="n">
         <v>1</v>
       </c>
+      <c r="AA68" t="n">
+        <v>0.9974454842158593</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.9244969012215734</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7518,6 +7930,12 @@
       <c r="Z69" t="n">
         <v>1</v>
       </c>
+      <c r="AA69" t="n">
+        <v>0.997301233233884</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0.8816817086189985</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7628,6 +8046,12 @@
       <c r="Z70" t="n">
         <v>1</v>
       </c>
+      <c r="AA70" t="n">
+        <v>0.9973319086711854</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.8892225408926606</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7730,6 +8154,12 @@
       <c r="Z71" t="n">
         <v>1</v>
       </c>
+      <c r="AA71" t="n">
+        <v>0.0001696998660918325</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-0.001096941530704498</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7832,6 +8262,12 @@
       <c r="Z72" t="n">
         <v>1</v>
       </c>
+      <c r="AA72" t="n">
+        <v>0.02515165146905929</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0.9108356544747949</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7934,6 +8370,12 @@
       <c r="Z73" t="n">
         <v>1</v>
       </c>
+      <c r="AA73" t="n">
+        <v>0.01250526253716089</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0.05985364504158497</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8036,6 +8478,12 @@
       <c r="Z74" t="n">
         <v>1</v>
       </c>
+      <c r="AA74" t="n">
+        <v>0.970862602640409</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.2102087344974279</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8138,6 +8586,12 @@
       <c r="Z75" t="n">
         <v>1</v>
       </c>
+      <c r="AA75" t="n">
+        <v>0.9974277083820198</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2812598701566458</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8240,6 +8694,12 @@
       <c r="Z76" t="n">
         <v>1</v>
       </c>
+      <c r="AA76" t="n">
+        <v>0.9974333831924014</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0.3231742810457945</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8342,6 +8802,12 @@
       <c r="Z77" t="n">
         <v>1</v>
       </c>
+      <c r="AA77" t="n">
+        <v>0.009518162813037634</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>0.06004118826240301</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8444,6 +8910,12 @@
       <c r="Z78" t="n">
         <v>1</v>
       </c>
+      <c r="AA78" t="n">
+        <v>0.9976746919564903</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>0.8741686078719795</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8546,6 +9018,12 @@
       <c r="Z79" t="n">
         <v>1</v>
       </c>
+      <c r="AA79" t="n">
+        <v>0.9907442391559016</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>0.1437234589830041</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8648,6 +9126,12 @@
       <c r="Z80" t="n">
         <v>1</v>
       </c>
+      <c r="AA80" t="n">
+        <v>0.9976469621178694</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.0370225515216589</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8750,6 +9234,12 @@
       <c r="Z81" t="n">
         <v>1</v>
       </c>
+      <c r="AA81" t="n">
+        <v>0.547125681056059</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.2130356058478355</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8852,6 +9342,12 @@
       <c r="Z82" t="n">
         <v>1</v>
       </c>
+      <c r="AA82" t="n">
+        <v>0.9969738363288343</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>0.8929161205887794</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8954,6 +9450,12 @@
       <c r="Z83" t="n">
         <v>1</v>
       </c>
+      <c r="AA83" t="n">
+        <v>0.9973008271190338</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0.6640588482841849</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9056,6 +9558,12 @@
       <c r="Z84" t="n">
         <v>1</v>
       </c>
+      <c r="AA84" t="n">
+        <v>0.9963770473550539</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>0.2197707472369075</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9158,6 +9666,12 @@
       <c r="Z85" t="n">
         <v>1</v>
       </c>
+      <c r="AA85" t="n">
+        <v>0.8791919331997633</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>0.3631373923271894</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9260,6 +9774,12 @@
       <c r="Z86" t="n">
         <v>1</v>
       </c>
+      <c r="AA86" t="n">
+        <v>0.9972335746278986</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>0.6765993516892195</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9362,6 +9882,12 @@
       <c r="Z87" t="n">
         <v>1</v>
       </c>
+      <c r="AA87" t="n">
+        <v>0.5331567525863647</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0.7644183505326509</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9464,6 +9990,12 @@
       <c r="Z88" t="n">
         <v>1</v>
       </c>
+      <c r="AA88" t="n">
+        <v>0.9943803038768237</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0.7297116266563535</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9566,6 +10098,12 @@
       <c r="Z89" t="n">
         <v>1</v>
       </c>
+      <c r="AA89" t="n">
+        <v>0.9977551818592474</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0.8912058351561427</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9668,6 +10206,12 @@
       <c r="Z90" t="n">
         <v>1</v>
       </c>
+      <c r="AA90" t="n">
+        <v>0.997548314393498</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>0.8009113245643675</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9770,6 +10314,12 @@
       <c r="Z91" t="n">
         <v>1</v>
       </c>
+      <c r="AA91" t="n">
+        <v>0.9967484800436068</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>0.07800011616200209</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9872,6 +10422,12 @@
       <c r="Z92" t="n">
         <v>1</v>
       </c>
+      <c r="AA92" t="n">
+        <v>0.9974027328426018</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>0.1749958973377943</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9974,6 +10530,12 @@
       <c r="Z93" t="n">
         <v>1</v>
       </c>
+      <c r="AA93" t="n">
+        <v>9.386491728946567e-05</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>0.06542901042848825</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10076,6 +10638,12 @@
       <c r="Z94" t="n">
         <v>1</v>
       </c>
+      <c r="AA94" t="n">
+        <v>0.1030750539794099</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0.07166038546711206</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10182,6 +10750,12 @@
       <c r="Z95" t="n">
         <v>1</v>
       </c>
+      <c r="AA95" t="n">
+        <v>-0.9977553590142634</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>0.204482227563858</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10284,6 +10858,12 @@
       <c r="Z96" t="n">
         <v>1</v>
       </c>
+      <c r="AA96" t="n">
+        <v>0.9966309371229727</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>0.5124907977879047</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10386,6 +10966,12 @@
       <c r="Z97" t="n">
         <v>1</v>
       </c>
+      <c r="AA97" t="n">
+        <v>0.08881029463373125</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>0.3404317758977413</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10488,6 +11074,12 @@
       <c r="Z98" t="n">
         <v>1</v>
       </c>
+      <c r="AA98" t="n">
+        <v>0.9960872441297397</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>0.8549763178452849</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10598,6 +11190,12 @@
       <c r="Z99" t="n">
         <v>1</v>
       </c>
+      <c r="AA99" t="n">
+        <v>-0.02397080170339905</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>0.04021824151277542</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10700,6 +11298,12 @@
       <c r="Z100" t="n">
         <v>1</v>
       </c>
+      <c r="AA100" t="n">
+        <v>0.9975027862819843</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>0.5852123145014048</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10802,6 +11406,12 @@
       <c r="Z101" t="n">
         <v>1</v>
       </c>
+      <c r="AA101" t="n">
+        <v>0.9977127438178286</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>0.868297684006393</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10904,6 +11514,12 @@
       <c r="Z102" t="n">
         <v>1</v>
       </c>
+      <c r="AA102" t="n">
+        <v>0.9933067574165761</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0.8931763619184494</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11006,6 +11622,12 @@
       <c r="Z103" t="n">
         <v>1</v>
       </c>
+      <c r="AA103" t="n">
+        <v>0.9961661037232261</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0.7983825323171914</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11108,6 +11730,12 @@
       <c r="Z104" t="n">
         <v>1</v>
       </c>
+      <c r="AA104" t="n">
+        <v>0.9973777357954532</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0.2241974156349897</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11210,6 +11838,12 @@
       <c r="Z105" t="n">
         <v>1</v>
       </c>
+      <c r="AA105" t="n">
+        <v>0.9973229372990318</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0.1047205552458763</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11312,6 +11946,12 @@
       <c r="Z106" t="n">
         <v>1</v>
       </c>
+      <c r="AA106" t="n">
+        <v>0.997523344180081</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0.5469032377004623</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11414,6 +12054,12 @@
       <c r="Z107" t="n">
         <v>1</v>
       </c>
+      <c r="AA107" t="n">
+        <v>0.9973542938241735</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>-0.005721520632505417</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11516,6 +12162,12 @@
       <c r="Z108" t="n">
         <v>1</v>
       </c>
+      <c r="AA108" t="n">
+        <v>0.9974553060601465</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0.8352093966677785</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11619,6 +12271,12 @@
       <c r="Z109" t="n">
         <v>1</v>
       </c>
+      <c r="AA109" t="n">
+        <v>0.9789626137644518</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0.07170799933373928</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11722,6 +12380,12 @@
       <c r="Z110" t="n">
         <v>1</v>
       </c>
+      <c r="AA110" t="n">
+        <v>0.9972009431221522</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0.1577191594988108</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11824,6 +12488,12 @@
       <c r="Z111" t="n">
         <v>1</v>
       </c>
+      <c r="AA111" t="n">
+        <v>0.1179338204383384</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0.5810780879110098</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11926,6 +12596,12 @@
       <c r="Z112" t="n">
         <v>1</v>
       </c>
+      <c r="AA112" t="n">
+        <v>0.9976423958723899</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0.8046755352988839</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12028,6 +12704,12 @@
       <c r="Z113" t="n">
         <v>1</v>
       </c>
+      <c r="AA113" t="n">
+        <v>0.9973418046138249</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0.7148459060117602</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12130,6 +12812,12 @@
       <c r="Z114" t="n">
         <v>1</v>
       </c>
+      <c r="AA114" t="n">
+        <v>0.9976279775146395</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0.8483454771339893</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12240,6 +12928,12 @@
       <c r="Z115" t="n">
         <v>1</v>
       </c>
+      <c r="AA115" t="n">
+        <v>0.9974510679603554</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0.7445605648681521</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12342,6 +13036,12 @@
       <c r="Z116" t="n">
         <v>1</v>
       </c>
+      <c r="AA116" t="n">
+        <v>0.0004109460569452494</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0.0007492117583751678</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12444,6 +13144,12 @@
       <c r="Z117" t="n">
         <v>1</v>
       </c>
+      <c r="AA117" t="n">
+        <v>0.9976081947679631</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4364009574055672</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12547,6 +13253,12 @@
       <c r="Z118" t="n">
         <v>1</v>
       </c>
+      <c r="AA118" t="n">
+        <v>0.9911714672052767</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.135175721719861</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12649,6 +13361,12 @@
       <c r="Z119" t="n">
         <v>1</v>
       </c>
+      <c r="AA119" t="n">
+        <v>0.9963163604406873</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.2393357548862696</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12751,6 +13469,12 @@
       <c r="Z120" t="n">
         <v>1</v>
       </c>
+      <c r="AA120" t="n">
+        <v>0.997686784772668</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.05628449376672506</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12853,6 +13577,12 @@
       <c r="Z121" t="n">
         <v>1</v>
       </c>
+      <c r="AA121" t="n">
+        <v>0.9967650202743243</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.2980295978486538</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12955,6 +13685,12 @@
       <c r="Z122" t="n">
         <v>1</v>
       </c>
+      <c r="AA122" t="n">
+        <v>0.9970536585315131</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.2571759531274438</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -13057,6 +13793,12 @@
       <c r="Z123" t="n">
         <v>1</v>
       </c>
+      <c r="AA123" t="n">
+        <v>0.9971934328787029</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.1162941455841064</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -13159,6 +13901,12 @@
       <c r="Z124" t="n">
         <v>1</v>
       </c>
+      <c r="AA124" t="n">
+        <v>0.0001604317803867161</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>-0.04314210638403893</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13261,6 +14009,12 @@
       <c r="Z125" t="n">
         <v>1</v>
       </c>
+      <c r="AA125" t="n">
+        <v>0.9974415731849149</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.8643737165257335</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13363,6 +14117,12 @@
       <c r="Z126" t="n">
         <v>1</v>
       </c>
+      <c r="AA126" t="n">
+        <v>0.9974708442750853</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.6471072514541447</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13465,6 +14225,12 @@
       <c r="Z127" t="n">
         <v>1</v>
       </c>
+      <c r="AA127" t="n">
+        <v>-4.267090116627514e-05</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.1112456182017922</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13567,6 +14333,12 @@
       <c r="Z128" t="n">
         <v>1</v>
       </c>
+      <c r="AA128" t="n">
+        <v>-8.952664211392403e-05</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.08915476128458977</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13669,6 +14441,12 @@
       <c r="Z129" t="n">
         <v>1</v>
       </c>
+      <c r="AA129" t="n">
+        <v>0.001426850431016646</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.059789446182549</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13771,6 +14549,12 @@
       <c r="Z130" t="n">
         <v>1</v>
       </c>
+      <c r="AA130" t="n">
+        <v>0.9975889538181946</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.7125622406601906</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13873,6 +14657,12 @@
       <c r="Z131" t="n">
         <v>1</v>
       </c>
+      <c r="AA131" t="n">
+        <v>0.9974599155830219</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.5329955900087953</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13975,6 +14765,12 @@
       <c r="Z132" t="n">
         <v>1</v>
       </c>
+      <c r="AA132" t="n">
+        <v>0.9975406192825176</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.8950422597117722</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14077,6 +14873,12 @@
       <c r="Z133" t="n">
         <v>1</v>
       </c>
+      <c r="AA133" t="n">
+        <v>-0.00272418512031436</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.03701310232281685</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14179,6 +14981,12 @@
       <c r="Z134" t="n">
         <v>1</v>
       </c>
+      <c r="AA134" t="n">
+        <v>0.9968178899143822</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.8032926744781435</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14281,6 +15089,12 @@
       <c r="Z135" t="n">
         <v>1</v>
       </c>
+      <c r="AA135" t="n">
+        <v>-0.0006178005132824183</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.06543170288205147</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14383,6 +15197,12 @@
       <c r="Z136" t="n">
         <v>1</v>
       </c>
+      <c r="AA136" t="n">
+        <v>0.9596819480793783</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.8951177014969289</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14485,6 +15305,12 @@
       <c r="Z137" t="n">
         <v>1</v>
       </c>
+      <c r="AA137" t="n">
+        <v>0.9381049093790352</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.6097705643624067</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14587,6 +15413,12 @@
       <c r="Z138" t="n">
         <v>1</v>
       </c>
+      <c r="AA138" t="n">
+        <v>0.9976650166790932</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.7616871893405914</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14689,6 +15521,12 @@
       <c r="Z139" t="n">
         <v>1</v>
       </c>
+      <c r="AA139" t="n">
+        <v>0.00573836755938828</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.003850042819976807</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14791,6 +15629,12 @@
       <c r="Z140" t="n">
         <v>1</v>
       </c>
+      <c r="AA140" t="n">
+        <v>0.002276976723806001</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.2716333782300353</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14893,6 +15737,12 @@
       <c r="Z141" t="n">
         <v>1</v>
       </c>
+      <c r="AA141" t="n">
+        <v>0.9327901387005113</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.4419217398390174</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14995,6 +15845,12 @@
       <c r="Z142" t="n">
         <v>1</v>
       </c>
+      <c r="AA142" t="n">
+        <v>0.06731412949739024</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.4139588214457035</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15097,6 +15953,12 @@
       <c r="Z143" t="n">
         <v>1</v>
       </c>
+      <c r="AA143" t="n">
+        <v>0.000798736436991021</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.006465688347816467</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15199,6 +16061,12 @@
       <c r="Z144" t="n">
         <v>1</v>
       </c>
+      <c r="AA144" t="n">
+        <v>0.9968401277146768</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0.0899457223713398</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15301,6 +16169,12 @@
       <c r="Z145" t="n">
         <v>1</v>
       </c>
+      <c r="AA145" t="n">
+        <v>0.9971181409200653</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0.5412873020395637</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15403,6 +16277,12 @@
       <c r="Z146" t="n">
         <v>1</v>
       </c>
+      <c r="AA146" t="n">
+        <v>0.00569297127367463</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>-0.004055056720972061</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15505,6 +16385,12 @@
       <c r="Z147" t="n">
         <v>1</v>
       </c>
+      <c r="AA147" t="n">
+        <v>0.995232188157388</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0.1287417216226459</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15607,6 +16493,12 @@
       <c r="Z148" t="n">
         <v>1</v>
       </c>
+      <c r="AA148" t="n">
+        <v>0.7776398229034385</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0.2928161146119237</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15709,6 +16601,12 @@
       <c r="Z149" t="n">
         <v>1</v>
       </c>
+      <c r="AA149" t="n">
+        <v>0.01262870887876488</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0.05362608283758163</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15820,6 +16718,12 @@
       <c r="Z150" t="n">
         <v>1</v>
       </c>
+      <c r="AA150" t="n">
+        <v>0.9975281041697599</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0.6994513645768166</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15922,6 +16826,12 @@
       <c r="Z151" t="n">
         <v>1</v>
       </c>
+      <c r="AA151" t="n">
+        <v>0.002583475405117497</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0.03652243502438068</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -16024,6 +16934,12 @@
       <c r="Z152" t="n">
         <v>1</v>
       </c>
+      <c r="AA152" t="n">
+        <v>0.0005027663573855534</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>-0.013196075335145</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -16126,6 +17042,12 @@
       <c r="Z153" t="n">
         <v>1</v>
       </c>
+      <c r="AA153" t="n">
+        <v>0.0006889772485010326</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0.05918855499476194</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -16228,6 +17150,12 @@
       <c r="Z154" t="n">
         <v>1</v>
       </c>
+      <c r="AA154" t="n">
+        <v>0.001194361480884254</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>-0.01157568208873272</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16330,6 +17258,12 @@
       <c r="Z155" t="n">
         <v>1</v>
       </c>
+      <c r="AA155" t="n">
+        <v>0.9976087939867284</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0.503469942137599</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -16432,6 +17366,12 @@
       <c r="Z156" t="n">
         <v>1</v>
       </c>
+      <c r="AA156" t="n">
+        <v>0.002127128274878487</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0.01484375819563866</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16534,6 +17474,12 @@
       <c r="Z157" t="n">
         <v>1</v>
       </c>
+      <c r="AA157" t="n">
+        <v>0.9974341045890469</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0.9184441063553095</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16636,6 +17582,12 @@
       <c r="Z158" t="n">
         <v>1</v>
       </c>
+      <c r="AA158" t="n">
+        <v>0.9892178555601276</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0.04182502627372742</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16738,6 +17690,12 @@
       <c r="Z159" t="n">
         <v>1</v>
       </c>
+      <c r="AA159" t="n">
+        <v>0.9819995034486055</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>0.3310967367142439</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16840,6 +17798,12 @@
       <c r="Z160" t="n">
         <v>1</v>
       </c>
+      <c r="AA160" t="n">
+        <v>0.00340110925026238</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>0.04028161242604256</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16942,6 +17906,12 @@
       <c r="Z161" t="n">
         <v>1</v>
       </c>
+      <c r="AA161" t="n">
+        <v>0.004940243190503679</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0.02749005146324635</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -17044,6 +18014,12 @@
       <c r="Z162" t="n">
         <v>1</v>
       </c>
+      <c r="AA162" t="n">
+        <v>0.001721787732094526</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0.08363029733300209</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -17146,6 +18122,12 @@
       <c r="Z163" t="n">
         <v>1</v>
       </c>
+      <c r="AA163" t="n">
+        <v>0.9976136330515146</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0.8785871588625014</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -17248,6 +18230,12 @@
       <c r="Z164" t="n">
         <v>1</v>
       </c>
+      <c r="AA164" t="n">
+        <v>0.9829498227336444</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0.2248738347552717</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -17350,6 +18338,12 @@
       <c r="Z165" t="n">
         <v>1</v>
       </c>
+      <c r="AA165" t="n">
+        <v>0.9975594207062386</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>0.8446468533948064</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -17452,6 +18446,12 @@
       <c r="Z166" t="n">
         <v>1</v>
       </c>
+      <c r="AA166" t="n">
+        <v>-0.9276563823223114</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>-0.05105102807283401</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -17554,6 +18554,12 @@
       <c r="Z167" t="n">
         <v>1</v>
       </c>
+      <c r="AA167" t="n">
+        <v>0.996669681800995</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0.3035414135083556</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17656,6 +18662,12 @@
       <c r="Z168" t="n">
         <v>1</v>
       </c>
+      <c r="AA168" t="n">
+        <v>3.468667273409665e-05</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>0.02904764655977488</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17758,6 +18770,12 @@
       <c r="Z169" t="n">
         <v>1</v>
       </c>
+      <c r="AA169" t="n">
+        <v>0.9974949929746799</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>0.8874865584075451</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17860,6 +18878,12 @@
       <c r="Z170" t="n">
         <v>1</v>
       </c>
+      <c r="AA170" t="n">
+        <v>0.9976717591052875</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>0.9045442277565598</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17962,6 +18986,12 @@
       <c r="Z171" t="n">
         <v>1</v>
       </c>
+      <c r="AA171" t="n">
+        <v>0.0009991906699724495</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>0.6168781528249383</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -18064,6 +19094,12 @@
       <c r="Z172" t="n">
         <v>1</v>
       </c>
+      <c r="AA172" t="n">
+        <v>0.9973593289032578</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>0.05307696387171745</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -18166,6 +19202,12 @@
       <c r="Z173" t="n">
         <v>1</v>
       </c>
+      <c r="AA173" t="n">
+        <v>0.9976528612314723</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>0.8496497669257224</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -18268,6 +19310,12 @@
       <c r="Z174" t="n">
         <v>1</v>
       </c>
+      <c r="AA174" t="n">
+        <v>-0.0001142718392657116</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>0.03769505303353071</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -18370,6 +19418,12 @@
       <c r="Z175" t="n">
         <v>1</v>
       </c>
+      <c r="AA175" t="n">
+        <v>0.0004487694823183119</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>0.1416234597563744</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -18472,6 +19526,12 @@
       <c r="Z176" t="n">
         <v>1</v>
       </c>
+      <c r="AA176" t="n">
+        <v>0.000453043554443866</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>0.03195302188396454</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -18574,6 +19634,12 @@
       <c r="Z177" t="n">
         <v>1</v>
       </c>
+      <c r="AA177" t="n">
+        <v>0.9971168868651148</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>0.1505423821508884</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -18676,6 +19742,12 @@
       <c r="Z178" t="n">
         <v>1</v>
       </c>
+      <c r="AA178" t="n">
+        <v>0.9974892644095235</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>0.8130631018429995</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18778,6 +19850,12 @@
       <c r="Z179" t="n">
         <v>1</v>
       </c>
+      <c r="AA179" t="n">
+        <v>0.997468325891532</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>0.4312223689630628</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18880,6 +19958,12 @@
       <c r="Z180" t="n">
         <v>1</v>
       </c>
+      <c r="AA180" t="n">
+        <v>-0.002130308595951647</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>0.1205633766949177</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18982,6 +20066,12 @@
       <c r="Z181" t="n">
         <v>1</v>
       </c>
+      <c r="AA181" t="n">
+        <v>0.1314152617705986</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>0.01802188158035278</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -19092,6 +20182,12 @@
       <c r="Z182" t="n">
         <v>1</v>
       </c>
+      <c r="AA182" t="n">
+        <v>0.05375529304728843</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>0.2691120868548751</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -19194,6 +20290,12 @@
       <c r="Z183" t="n">
         <v>1</v>
       </c>
+      <c r="AA183" t="n">
+        <v>0.9974800891068298</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>0.1562981177121401</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -19296,6 +20398,12 @@
       <c r="Z184" t="n">
         <v>1</v>
       </c>
+      <c r="AA184" t="n">
+        <v>0.02584114228375256</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>-0.006036002188920975</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -19398,6 +20506,12 @@
       <c r="Z185" t="n">
         <v>1</v>
       </c>
+      <c r="AA185" t="n">
+        <v>0.9582349400880048</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>0.08649146649986506</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -19500,6 +20614,12 @@
       <c r="Z186" t="n">
         <v>1</v>
       </c>
+      <c r="AA186" t="n">
+        <v>0.9962305914377794</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>0.1445936094969511</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -19602,6 +20722,12 @@
       <c r="Z187" t="n">
         <v>1</v>
       </c>
+      <c r="AA187" t="n">
+        <v>0.99751187505899</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>0.6295274281874299</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19704,6 +20830,12 @@
       <c r="Z188" t="n">
         <v>1</v>
       </c>
+      <c r="AA188" t="n">
+        <v>0.0001548155123600736</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>0.04500133357942104</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19806,6 +20938,12 @@
       <c r="Z189" t="n">
         <v>1</v>
       </c>
+      <c r="AA189" t="n">
+        <v>0.9973124918760732</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>0.9417950324714184</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19908,6 +21046,12 @@
       <c r="Z190" t="n">
         <v>1</v>
       </c>
+      <c r="AA190" t="n">
+        <v>0.997539609670639</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>0.9341408647596836</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -20010,6 +21154,12 @@
       <c r="Z191" t="n">
         <v>1</v>
       </c>
+      <c r="AA191" t="n">
+        <v>0.9975560691673309</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>0.7073978930711746</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -20112,6 +21262,12 @@
       <c r="Z192" t="n">
         <v>1</v>
       </c>
+      <c r="AA192" t="n">
+        <v>0.9975561117753386</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>0.9209807403385639</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -20215,6 +21371,12 @@
       <c r="Z193" t="n">
         <v>1</v>
       </c>
+      <c r="AA193" t="n">
+        <v>0.9975532976677641</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>0.9331726394593716</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -20318,6 +21480,12 @@
       <c r="Z194" t="n">
         <v>1</v>
       </c>
+      <c r="AA194" t="n">
+        <v>0.9975211911951192</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>0.925104477442801</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -20420,6 +21588,12 @@
       <c r="Z195" t="n">
         <v>1</v>
       </c>
+      <c r="AA195" t="n">
+        <v>0.004473072578548454</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>0.07979044504463673</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -20522,6 +21696,12 @@
       <c r="Z196" t="n">
         <v>1</v>
       </c>
+      <c r="AA196" t="n">
+        <v>0.9970210393657908</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>0.4863830395042896</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -20624,6 +21804,12 @@
       <c r="Z197" t="n">
         <v>1</v>
       </c>
+      <c r="AA197" t="n">
+        <v>0.9976772735826671</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>0.8742589270696044</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20726,6 +21912,12 @@
       <c r="Z198" t="n">
         <v>1</v>
       </c>
+      <c r="AA198" t="n">
+        <v>8.850650920066983e-05</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>-0.03471975773572922</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -20828,6 +22020,12 @@
       <c r="Z199" t="n">
         <v>1</v>
       </c>
+      <c r="AA199" t="n">
+        <v>0.32271212998603</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>0.05185882747173309</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20930,6 +22128,12 @@
       <c r="Z200" t="n">
         <v>1</v>
       </c>
+      <c r="AA200" t="n">
+        <v>0.9973829265800305</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>0.7951832301914692</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -21032,6 +22236,12 @@
       <c r="Z201" t="n">
         <v>1</v>
       </c>
+      <c r="AA201" t="n">
+        <v>0.0003227547858841717</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>0.05257809720933437</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -21134,6 +22344,12 @@
       <c r="Z202" t="n">
         <v>1</v>
       </c>
+      <c r="AA202" t="n">
+        <v>0.9973034960275982</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>0.3986655855551362</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -21236,6 +22452,12 @@
       <c r="Z203" t="n">
         <v>1</v>
       </c>
+      <c r="AA203" t="n">
+        <v>-0.9923790817847475</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>0.4175728233531117</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -21338,6 +22560,12 @@
       <c r="Z204" t="n">
         <v>1</v>
       </c>
+      <c r="AA204" t="n">
+        <v>0.9970620272215456</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>0.6944117825478315</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -21440,6 +22668,12 @@
       <c r="Z205" t="n">
         <v>1</v>
       </c>
+      <c r="AA205" t="n">
+        <v>0.9974371528369375</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0.6677299095317721</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -21542,6 +22776,12 @@
       <c r="Z206" t="n">
         <v>1</v>
       </c>
+      <c r="AA206" t="n">
+        <v>0.9977174300292972</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>0.7892404096201062</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -21643,6 +22883,12 @@
       </c>
       <c r="Z207" t="n">
         <v>1</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>0.997571115323808</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>0.8858713191002607</v>
       </c>
     </row>
   </sheetData>
